--- a/assets/constructions/examples/ctd_ds5.xlsx
+++ b/assets/constructions/examples/ctd_ds5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,36 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>121110 12</t>
+          <t>111300 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -593,25 +618,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>121110</t>
+          <t>111300</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PMKN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>h7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -623,7 +648,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -636,25 +661,21 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>142</v>
-      </c>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="U2" t="n">
-        <v>70</v>
-      </c>
-      <c r="V2" t="n">
-        <v>24</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
@@ -667,57 +688,68 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>k12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>HB-12</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6290-d4</t>
+          <t>121070 3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>GARANT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>121070</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.45</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>h7</t>
+          <t>h6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -725,11 +757,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
@@ -746,21 +774,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>142</v>
+      </c>
       <c r="T3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="U3" t="n">
-        <v>56</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8</v>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
@@ -768,76 +800,89 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2017/ilix-polnyy-katalog-instrumenta-2017-en</t>
+          <t>2020 / hoffmann-group.ru</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>HSS</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-3</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>PN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DCACE0130U</t>
+          <t>5140250</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMATI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DCAC</t>
-        </is>
-      </c>
+          <t>GABRIEL MAUVAIS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.85</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>h5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A120</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Super MG</t>
+          <t>HSS-Co</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Super MG</t>
+          <t>HSS-Co</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>TISIN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -850,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -861,13 +906,13 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U4" t="n">
-        <v>48.874</v>
+        <v>24.278</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -876,34 +921,41 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2023/Amati Форма Точности</t>
+          <t>2015 / GABRIEL MAUVAIS Catalog</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>VHM</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>m7</t>
-        </is>
-      </c>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>HA-3</t>
+          <t>HA-2.5</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6292-d3.15</t>
+          <t>6162TN-d0.75</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -913,7 +965,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -923,11 +975,9 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.25</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
@@ -936,18 +986,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -960,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -969,10 +1019,10 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -993,42 +1043,53 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-3.5</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>111105 3,15</t>
+          <t>6296-d0.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GARANT</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>111105</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.575</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -1045,7 +1106,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1053,16 +1114,12 @@
           <t>R</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>DIN 333</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1071,10 +1128,10 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="U6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1084,27 +1141,34 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2020 / hoffmann-group.ru</t>
+          <t>2017/ilix-polnyy-katalog-instrumenta-2017-en</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>HSS</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>k12</t>
-        </is>
-      </c>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-3.15</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
